--- a/results/Int All Data -0.4/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.4/Linea_fi_all.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.0038876889848811656 +/- 0.0006926857241790717</t>
+          <t>0.003918543659364349 +/- 0.0006624779559883992</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>0.01295896328293733 +/- 0.004284246826957067</t>
+          <t>0.012928108608454147 +/- 0.004254030548813579</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.00023894862604538768 +/- 0.00022351597292553745</t>
+          <t>-5.9737156511352477e-05 +/- 0.00011947431302270495</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>2.9868578255687338e-05 +/- 0.00045199360664341116</t>
+          <t>5.9737156511363576e-05 +/- 0.00045884980572691346</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-0.00943847072879327 +/- 0.0014336917562723964</t>
+          <t>-0.009468339307048945 +/- 0.0014451577542894751</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0034348864994026675 +/- 0.0013638530533848145</t>
+          <t>0.003405017921146991 +/- 0.0013370985236319838</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>0.03312425328554365 +/- 0.006759081734887573</t>
+          <t>0.03309438470728797 +/- 0.006739717444563628</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.005642440969027884 +/- 0.0014526487926804132</t>
+          <t>0.005703771849126016 +/- 0.0014066047152627842</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0006133088009813048 +/- 0.0008453878412812256</t>
+          <t>-0.0005826433609322446 +/- 0.0008503786951157423</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.08070841239721693 +/- 0.0030850723335249133</t>
+          <t>0.08061353573687538 +/- 0.0030117424850234172</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.03697688944409747 +/- 0.0023669325823231164</t>
+          <t>0.03700811992504688 +/- 0.0023255701675367387</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.006253928346951565 +/- 0.00129156018780857</t>
+          <t>-0.006222501571338734 +/- 0.001286580106251322</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.00053425518541802 +/- 0.0004671926067667599</t>
+          <t>0.0005028284098052005 +/- 0.0004703529084568038</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>-0.012697466467958263 +/- 0.0019325860002917807</t>
+          <t>-0.012667660208643804 +/- 0.001881575451813602</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.00080102531239985 +/- 0.00041157425756698835</t>
+          <t>-0.0007689842999038521 +/- 0.0004103251674100063</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
